--- a/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_nsw.xlsx
+++ b/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_nsw.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="467" documentId="11_BAEBAB7BF539ECEFC4DE0B80F93993E438A4C42B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{524C9566-BDFF-4941-9974-B6E0FFFAD97A}"/>
+  <xr:revisionPtr revIDLastSave="480" documentId="11_BAEBAB7BF539ECEFC4DE0B80F93993E438A4C42B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E3DF325-578C-46F0-9174-12CE0D1B853D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Farm labels" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="373">
   <si>
     <t>source</t>
   </si>
@@ -646,6 +646,9 @@
   </si>
   <si>
     <t>Multiple Classes</t>
+  </si>
+  <si>
+    <t>Poultry/ Residential</t>
   </si>
   <si>
     <t>70234/buildings/Mangrove__EPSG3857_Date2023101_1.tif_farm_70234_building_6.tif</t>
@@ -2890,8 +2893,12 @@
       <c r="U26" s="5"/>
       <c r="V26" s="6"/>
       <c r="W26" s="5"/>
-      <c r="X26" s="6"/>
-      <c r="Y26" s="5"/>
+      <c r="X26" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y26" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Z26" s="6" t="s">
         <v>31</v>
       </c>
@@ -4921,7 +4928,6 @@
       <c r="AB71" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB71" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -6753,7 +6759,9 @@
       <c r="F85" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="G85" s="11"/>
+      <c r="G85" s="11" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="12" t="s">
@@ -6769,7 +6777,7 @@
         <v>30</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F86" s="14" t="s">
         <v>25</v>
@@ -6790,7 +6798,7 @@
         <v>30</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F87" s="6" t="s">
         <v>117</v>
@@ -6811,7 +6819,7 @@
         <v>30</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>21</v>
@@ -6832,7 +6840,7 @@
         <v>30</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F89" s="17" t="s">
         <v>21</v>
@@ -6853,7 +6861,7 @@
         <v>30</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F90" s="10" t="s">
         <v>117</v>
@@ -6874,7 +6882,7 @@
         <v>30</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>117</v>
@@ -6895,7 +6903,7 @@
         <v>30</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F92" s="10" t="s">
         <v>25</v>
@@ -6916,7 +6924,7 @@
         <v>30</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>117</v>
@@ -6937,7 +6945,7 @@
         <v>30</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F94" s="14" t="s">
         <v>117</v>
@@ -6958,7 +6966,7 @@
         <v>30</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>120</v>
@@ -6979,7 +6987,7 @@
         <v>30</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>117</v>
@@ -7000,7 +7008,7 @@
         <v>30</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>120</v>
@@ -7021,7 +7029,7 @@
         <v>30</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>117</v>
@@ -7042,7 +7050,7 @@
         <v>30</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>120</v>
@@ -7063,7 +7071,7 @@
         <v>30</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7084,7 +7092,7 @@
         <v>30</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F101" s="17" t="s">
         <v>47</v>
@@ -7105,7 +7113,7 @@
         <v>30</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F102" s="10" t="s">
         <v>117</v>
@@ -7126,7 +7134,7 @@
         <v>30</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>117</v>
@@ -7147,7 +7155,7 @@
         <v>30</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F104" s="10" t="s">
         <v>47</v>
@@ -7168,7 +7176,7 @@
         <v>30</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F105" s="14" t="s">
         <v>117</v>
@@ -7189,12 +7197,14 @@
         <v>30</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="G106" s="7"/>
+      <c r="G106" s="11" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="4" t="s">
@@ -7210,7 +7220,7 @@
         <v>30</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>117</v>
@@ -7231,7 +7241,7 @@
         <v>30</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>9</v>
@@ -7252,7 +7262,7 @@
         <v>30</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>9</v>
@@ -7273,7 +7283,7 @@
         <v>30</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>120</v>
@@ -7294,7 +7304,7 @@
         <v>30</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>117</v>
@@ -7315,7 +7325,7 @@
         <v>30</v>
       </c>
       <c r="E112" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F112" s="17" t="s">
         <v>25</v>
@@ -7336,7 +7346,7 @@
         <v>30</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>47</v>
@@ -7357,7 +7367,7 @@
         <v>30</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F114" s="14" t="s">
         <v>25</v>
@@ -7378,7 +7388,7 @@
         <v>30</v>
       </c>
       <c r="E115" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F115" s="17" t="s">
         <v>120</v>
@@ -7399,7 +7409,7 @@
         <v>30</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F116" s="14" t="s">
         <v>25</v>
@@ -7420,7 +7430,7 @@
         <v>30</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>117</v>
@@ -7441,7 +7451,7 @@
         <v>30</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>117</v>
@@ -7462,7 +7472,7 @@
         <v>30</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>117</v>
@@ -7483,7 +7493,7 @@
         <v>30</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>47</v>
@@ -7504,7 +7514,7 @@
         <v>30</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>117</v>
@@ -7525,7 +7535,7 @@
         <v>30</v>
       </c>
       <c r="E122" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F122" s="17" t="s">
         <v>47</v>
@@ -7546,7 +7556,7 @@
         <v>30</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>9</v>
@@ -7567,7 +7577,7 @@
         <v>30</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F124" s="14" t="s">
         <v>25</v>
@@ -7588,7 +7598,7 @@
         <v>30</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F125" s="6" t="s">
         <v>117</v>
@@ -7609,7 +7619,7 @@
         <v>30</v>
       </c>
       <c r="E126" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F126" s="17" t="s">
         <v>11</v>
@@ -7630,7 +7640,7 @@
         <v>30</v>
       </c>
       <c r="E127" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F127" s="14" t="s">
         <v>11</v>
@@ -7651,7 +7661,7 @@
         <v>30</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>11</v>
@@ -7672,7 +7682,7 @@
         <v>30</v>
       </c>
       <c r="E129" s="16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F129" s="17" t="s">
         <v>120</v>
@@ -7693,7 +7703,7 @@
         <v>30</v>
       </c>
       <c r="E130" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F130" s="14" t="s">
         <v>9</v>
@@ -7714,7 +7724,7 @@
         <v>30</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>11</v>
@@ -7735,7 +7745,7 @@
         <v>30</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>120</v>
@@ -7756,7 +7766,7 @@
         <v>30</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F133" s="6" t="s">
         <v>11</v>
@@ -7777,7 +7787,7 @@
         <v>30</v>
       </c>
       <c r="E134" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F134" s="17" t="s">
         <v>117</v>
@@ -7798,7 +7808,7 @@
         <v>30</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>25</v>
@@ -7819,7 +7829,7 @@
         <v>30</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F136" s="10" t="s">
         <v>21</v>
@@ -7840,7 +7850,7 @@
         <v>30</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>25</v>
@@ -7861,7 +7871,7 @@
         <v>30</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F138" s="10" t="s">
         <v>21</v>
@@ -7882,7 +7892,7 @@
         <v>30</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>25</v>
@@ -7903,7 +7913,7 @@
         <v>30</v>
       </c>
       <c r="E140" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F140" s="14" t="s">
         <v>21</v>
@@ -7924,7 +7934,7 @@
         <v>30</v>
       </c>
       <c r="E141" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F141" s="17" t="s">
         <v>47</v>
@@ -7945,7 +7955,7 @@
         <v>30</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F142" s="10" t="s">
         <v>11</v>
@@ -7966,7 +7976,7 @@
         <v>30</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>117</v>
@@ -7987,7 +7997,7 @@
         <v>30</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F144" s="10" t="s">
         <v>117</v>
@@ -8008,7 +8018,7 @@
         <v>30</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F145" s="14" t="s">
         <v>11</v>
@@ -8029,7 +8039,7 @@
         <v>30</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>23</v>
@@ -8050,7 +8060,7 @@
         <v>30</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F147" s="6" t="s">
         <v>117</v>
@@ -8071,7 +8081,7 @@
         <v>30</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>23</v>
@@ -8092,7 +8102,7 @@
         <v>30</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F149" s="6" t="s">
         <v>25</v>
@@ -8113,7 +8123,7 @@
         <v>30</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>23</v>
@@ -8134,7 +8144,7 @@
         <v>30</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F151" s="6" t="s">
         <v>117</v>
@@ -8155,7 +8165,7 @@
         <v>30</v>
       </c>
       <c r="E152" s="16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F152" s="17" t="s">
         <v>25</v>
@@ -8176,7 +8186,7 @@
         <v>30</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F153" s="14" t="s">
         <v>25</v>
@@ -8197,7 +8207,7 @@
         <v>30</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>9</v>
@@ -8218,7 +8228,7 @@
         <v>30</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F155" s="6" t="s">
         <v>117</v>
@@ -8239,7 +8249,7 @@
         <v>30</v>
       </c>
       <c r="E156" s="16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F156" s="17" t="s">
         <v>117</v>
@@ -8260,7 +8270,7 @@
         <v>30</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F157" s="14" t="s">
         <v>47</v>
@@ -8281,7 +8291,7 @@
         <v>30</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>11</v>
@@ -8302,7 +8312,7 @@
         <v>30</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F159" s="6" t="s">
         <v>117</v>
@@ -8323,7 +8333,7 @@
         <v>30</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>11</v>
@@ -8344,7 +8354,7 @@
         <v>30</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F161" s="6" t="s">
         <v>117</v>
@@ -8365,7 +8375,7 @@
         <v>30</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>117</v>
@@ -8386,7 +8396,7 @@
         <v>30</v>
       </c>
       <c r="E163" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F163" s="17" t="s">
         <v>11</v>
@@ -8407,7 +8417,7 @@
         <v>23</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F164" s="10" t="s">
         <v>9</v>
@@ -8428,7 +8438,7 @@
         <v>23</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>117</v>
@@ -8449,7 +8459,7 @@
         <v>23</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F166" s="10" t="s">
         <v>9</v>
@@ -8470,7 +8480,7 @@
         <v>23</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>9</v>
@@ -8491,7 +8501,7 @@
         <v>23</v>
       </c>
       <c r="E168" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F168" s="10" t="s">
         <v>9</v>
@@ -8512,7 +8522,7 @@
         <v>23</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F169" s="14" t="s">
         <v>9</v>
@@ -8533,7 +8543,7 @@
         <v>30</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>11</v>
@@ -8554,7 +8564,7 @@
         <v>30</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>117</v>
@@ -8575,7 +8585,7 @@
         <v>30</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>117</v>
@@ -8596,7 +8606,7 @@
         <v>30</v>
       </c>
       <c r="E173" s="16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F173" s="17" t="s">
         <v>11</v>
@@ -8617,7 +8627,7 @@
         <v>30</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F174" s="10" t="s">
         <v>117</v>
@@ -8638,7 +8648,7 @@
         <v>30</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>25</v>
@@ -8659,7 +8669,7 @@
         <v>30</v>
       </c>
       <c r="E176" s="12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F176" s="14" t="s">
         <v>117</v>
@@ -8680,7 +8690,7 @@
         <v>89</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>11</v>
@@ -8701,7 +8711,7 @@
         <v>89</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>13</v>
@@ -8722,7 +8732,7 @@
         <v>89</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F179" s="6" t="s">
         <v>117</v>
@@ -8743,7 +8753,7 @@
         <v>89</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>11</v>
@@ -8764,7 +8774,7 @@
         <v>89</v>
       </c>
       <c r="E181" s="16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F181" s="17" t="s">
         <v>47</v>
@@ -8785,7 +8795,7 @@
         <v>30</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F182" s="10" t="s">
         <v>47</v>
@@ -8806,7 +8816,7 @@
         <v>30</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>117</v>
@@ -8827,7 +8837,7 @@
         <v>30</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F184" s="10" t="s">
         <v>117</v>
@@ -8848,7 +8858,7 @@
         <v>30</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>117</v>
@@ -8869,7 +8879,7 @@
         <v>30</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F186" s="10" t="s">
         <v>117</v>
@@ -8890,7 +8900,7 @@
         <v>30</v>
       </c>
       <c r="E187" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F187" s="14" t="s">
         <v>117</v>
@@ -8911,7 +8921,7 @@
         <v>30</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>11</v>
@@ -8932,7 +8942,7 @@
         <v>30</v>
       </c>
       <c r="E189" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F189" s="17" t="s">
         <v>11</v>
@@ -8953,7 +8963,7 @@
         <v>17</v>
       </c>
       <c r="E190" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F190" s="10" t="s">
         <v>25</v>
@@ -8974,7 +8984,7 @@
         <v>17</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>117</v>
@@ -8995,7 +9005,7 @@
         <v>17</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F192" s="10" t="s">
         <v>117</v>
@@ -9016,7 +9026,7 @@
         <v>17</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>117</v>
@@ -9037,7 +9047,7 @@
         <v>17</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F194" s="10" t="s">
         <v>11</v>
@@ -9058,7 +9068,7 @@
         <v>17</v>
       </c>
       <c r="E195" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>117</v>
@@ -9079,7 +9089,7 @@
         <v>17</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F196" s="10" t="s">
         <v>117</v>
@@ -9100,7 +9110,7 @@
         <v>17</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>25</v>
@@ -9121,7 +9131,7 @@
         <v>17</v>
       </c>
       <c r="E198" s="12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F198" s="14" t="s">
         <v>47</v>
@@ -9142,7 +9152,7 @@
         <v>30</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F199" s="6" t="s">
         <v>25</v>
@@ -9163,7 +9173,7 @@
         <v>30</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>117</v>
@@ -9184,7 +9194,7 @@
         <v>30</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F201" s="6" t="s">
         <v>117</v>
@@ -9205,7 +9215,7 @@
         <v>30</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>117</v>
@@ -9226,7 +9236,7 @@
         <v>30</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F203" s="6" t="s">
         <v>117</v>
@@ -9247,7 +9257,7 @@
         <v>30</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>9</v>
@@ -9268,7 +9278,7 @@
         <v>30</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F205" s="6" t="s">
         <v>25</v>
@@ -9289,7 +9299,7 @@
         <v>30</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>117</v>
@@ -9310,7 +9320,7 @@
         <v>30</v>
       </c>
       <c r="E207" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F207" s="17" t="s">
         <v>117</v>
@@ -9331,7 +9341,7 @@
         <v>30</v>
       </c>
       <c r="E208" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F208" s="14" t="s">
         <v>11</v>
@@ -9352,7 +9362,7 @@
         <v>30</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F209" s="6" t="s">
         <v>21</v>
@@ -9373,7 +9383,7 @@
         <v>30</v>
       </c>
       <c r="E210" s="16" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F210" s="17" t="s">
         <v>117</v>
@@ -9394,7 +9404,7 @@
         <v>30</v>
       </c>
       <c r="E211" s="12" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F211" s="14" t="s">
         <v>117</v>
@@ -9415,7 +9425,7 @@
         <v>30</v>
       </c>
       <c r="E212" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>11</v>
@@ -9436,7 +9446,7 @@
         <v>30</v>
       </c>
       <c r="E213" s="16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F213" s="17" t="s">
         <v>25</v>
@@ -9457,7 +9467,7 @@
         <v>30</v>
       </c>
       <c r="E214" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F214" s="14" t="s">
         <v>25</v>
@@ -9478,7 +9488,7 @@
         <v>30</v>
       </c>
       <c r="E215" s="16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F215" s="17" t="s">
         <v>25</v>
@@ -9499,7 +9509,7 @@
         <v>30</v>
       </c>
       <c r="E216" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F216" s="14" t="s">
         <v>21</v>
@@ -9520,7 +9530,7 @@
         <v>30</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F217" s="6" t="s">
         <v>11</v>
@@ -9541,7 +9551,7 @@
         <v>30</v>
       </c>
       <c r="E218" s="16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F218" s="17" t="s">
         <v>25</v>
@@ -9562,7 +9572,7 @@
         <v>30</v>
       </c>
       <c r="E219" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>47</v>
@@ -9583,7 +9593,7 @@
         <v>30</v>
       </c>
       <c r="E220" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F220" s="14" t="s">
         <v>25</v>
@@ -9604,7 +9614,7 @@
         <v>30</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F221" s="6" t="s">
         <v>11</v>
@@ -9625,7 +9635,7 @@
         <v>30</v>
       </c>
       <c r="E222" s="16" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F222" s="17" t="s">
         <v>25</v>
@@ -9646,7 +9656,7 @@
         <v>30</v>
       </c>
       <c r="E223" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>11</v>
@@ -9667,7 +9677,7 @@
         <v>30</v>
       </c>
       <c r="E224" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F224" s="10" t="s">
         <v>117</v>
@@ -9688,7 +9698,7 @@
         <v>30</v>
       </c>
       <c r="E225" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F225" s="14" t="s">
         <v>11</v>
@@ -9709,7 +9719,7 @@
         <v>30</v>
       </c>
       <c r="E226" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>117</v>
@@ -9730,7 +9740,7 @@
         <v>30</v>
       </c>
       <c r="E227" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F227" s="6" t="s">
         <v>11</v>
@@ -9751,7 +9761,7 @@
         <v>30</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>117</v>
@@ -9772,7 +9782,7 @@
         <v>30</v>
       </c>
       <c r="E229" s="16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F229" s="17" t="s">
         <v>11</v>
@@ -9793,7 +9803,7 @@
         <v>30</v>
       </c>
       <c r="E230" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F230" s="10" t="s">
         <v>25</v>
@@ -9814,7 +9824,7 @@
         <v>30</v>
       </c>
       <c r="E231" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F231" s="14" t="s">
         <v>11</v>
@@ -9835,7 +9845,7 @@
         <v>30</v>
       </c>
       <c r="E232" s="16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F232" s="17" t="s">
         <v>21</v>
@@ -9856,7 +9866,7 @@
         <v>30</v>
       </c>
       <c r="E233" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>9</v>
@@ -9877,7 +9887,7 @@
         <v>30</v>
       </c>
       <c r="E234" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F234" s="14" t="s">
         <v>25</v>
@@ -9898,7 +9908,7 @@
         <v>30</v>
       </c>
       <c r="E235" s="16" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F235" s="17" t="s">
         <v>25</v>
@@ -9919,7 +9929,7 @@
         <v>30</v>
       </c>
       <c r="E236" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F236" s="10" t="s">
         <v>117</v>
@@ -9940,7 +9950,7 @@
         <v>30</v>
       </c>
       <c r="E237" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>117</v>
@@ -9961,7 +9971,7 @@
         <v>30</v>
       </c>
       <c r="E238" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F238" s="10" t="s">
         <v>117</v>
@@ -9982,7 +9992,7 @@
         <v>30</v>
       </c>
       <c r="E239" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>117</v>
@@ -10003,7 +10013,7 @@
         <v>30</v>
       </c>
       <c r="E240" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F240" s="14" t="s">
         <v>25</v>
@@ -10024,7 +10034,7 @@
         <v>30</v>
       </c>
       <c r="E241" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F241" s="6" t="s">
         <v>23</v>
@@ -10045,7 +10055,7 @@
         <v>30</v>
       </c>
       <c r="E242" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>117</v>
@@ -10066,7 +10076,7 @@
         <v>30</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F243" s="6" t="s">
         <v>23</v>
@@ -10087,7 +10097,7 @@
         <v>30</v>
       </c>
       <c r="E244" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>120</v>
@@ -10108,7 +10118,7 @@
         <v>30</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F245" s="6" t="s">
         <v>47</v>
@@ -10129,7 +10139,7 @@
         <v>30</v>
       </c>
       <c r="E246" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>23</v>
@@ -10150,7 +10160,7 @@
         <v>30</v>
       </c>
       <c r="E247" s="16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F247" s="17" t="s">
         <v>25</v>
@@ -10171,7 +10181,7 @@
         <v>89</v>
       </c>
       <c r="E248" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F248" s="10" t="s">
         <v>17</v>
@@ -10192,7 +10202,7 @@
         <v>89</v>
       </c>
       <c r="E249" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>117</v>
@@ -10213,7 +10223,7 @@
         <v>89</v>
       </c>
       <c r="E250" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F250" s="10" t="s">
         <v>117</v>
@@ -10234,7 +10244,7 @@
         <v>89</v>
       </c>
       <c r="E251" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F251" s="14" t="s">
         <v>11</v>
@@ -10242,7 +10252,6 @@
       <c r="G251" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G251" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -10271,13 +10280,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="19" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -10600,15 +10609,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="73cbf0c7-d69e-427c-8bf4-4bd79e720451" xsi:nil="true"/>
@@ -10619,14 +10619,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59556458-AF5D-47FA-8AA5-1E6AC2BCB6C0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14E17ED4-8DA6-44DA-AA04-67A9EB7F9786}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18864E08-7FD6-4D23-AD4D-07BC60BBC295}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18864E08-7FD6-4D23-AD4D-07BC60BBC295}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14E17ED4-8DA6-44DA-AA04-67A9EB7F9786}"/>
 </file>
--- a/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_nsw.xlsx
+++ b/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_nsw.xlsx
@@ -593,8 +593,8 @@
   <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="22.42578125" customWidth="1" min="2" max="2"/>
+    <col width="22.42578125" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="9.5703125" customWidth="1" min="3" max="3"/>
     <col width="41.42578125" customWidth="1" min="4" max="4"/>
     <col width="9.7109375" customWidth="1" min="5" max="5"/>
@@ -622,12 +622,12 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Farm UID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
           <t>farm-952e3e7f9cce8bac</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
@@ -828,12 +828,12 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
           <t>farm-fb13b7efbe9e3f35</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -883,12 +883,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
           <t>farm-845d5252f2eca38f</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -954,12 +954,12 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
           <t>farm-78f45637e348bdaf</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -1017,12 +1017,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
           <t>farm-074eca694879aa6e</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -1084,12 +1084,12 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
           <t>farm-85691d9be362dd92</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -1147,12 +1147,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
           <t>farm-e1313b168a311d0b</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -1202,12 +1202,12 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
           <t>farm-d1deabe5ee33721b</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -1257,12 +1257,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>farm-9384fa5d4c771974</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -1320,12 +1320,12 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
           <t>farm-afc92ff8f440c5a0</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
@@ -1383,12 +1383,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>farm-2cde79d4f362fc20</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -1438,12 +1438,12 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
           <t>farm-b870c80169a03f88</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -1493,12 +1493,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
           <t>farm-8efe629438a3f81f</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -1556,12 +1556,12 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
           <t>farm-6bb3e077f36e38b2</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -1611,12 +1611,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>farm-f81d3c0b12219615</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -1666,12 +1666,12 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
           <t>farm-07b8ef74bb489456</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -1737,12 +1737,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>farm-54146e89a448bd06</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -1796,12 +1796,12 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
           <t>farm-e5c279f4236b6189</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
@@ -1851,12 +1851,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>farm-8bdf78650621db28</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -1910,12 +1910,12 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
           <t>farm-13959f39099f0e5f</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
@@ -1977,12 +1977,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t>farm-6fca13195dca72af</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -2036,12 +2036,12 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
           <t>farm-c3fc573e5c4acba5</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -2095,12 +2095,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>farm-c57fa3b9113fc7b7</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -2158,12 +2158,12 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
           <t>farm-79fc2a4c6da9eafa</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
@@ -2213,12 +2213,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
           <t>farm-f5449e374d877b37</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -2288,12 +2288,12 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
           <t>farm-e865e03867964311</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -2347,12 +2347,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>farm-a3294386b279337a</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -2402,12 +2402,12 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
           <t>farm-accb3fa2101c3789</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -2461,12 +2461,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>farm-abdbf0576da99c8b</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
@@ -2516,12 +2516,12 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
           <t>farm-cb9c2d243956a1cd</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -2583,12 +2583,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
           <t>farm-cf5621f1257fd08b</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
@@ -2642,12 +2642,12 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
           <t>farm-5abeeb94073a36a5</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -2701,12 +2701,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
           <t>farm-5043b3493257a17e</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
@@ -2760,12 +2760,12 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>farm-1c7e52d2eec151b1</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -2819,12 +2819,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>farm-739bcdfb546d7819</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
@@ -2878,12 +2878,12 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
           <t>farm-d2f56463641f55b6</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -2945,12 +2945,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>farm-aa14b1ecae53529a</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
@@ -3000,12 +3000,12 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
           <t>farm-2545beb9726fd83f</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -3059,12 +3059,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
           <t>farm-65eb57ca90edfc00</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
@@ -3126,12 +3126,12 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t>farm-f32dec1621b342da</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
@@ -3185,12 +3185,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>farm-316cd5378a884aec</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -3244,12 +3244,12 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
           <t>farm-a7055f2a67f08171</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -3299,12 +3299,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
           <t>farm-2d6c5d61d9cedd64</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -3358,12 +3358,12 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
           <t>farm-4e02cf1e777043d5</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -3417,12 +3417,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
           <t>farm-dea55e991a4e7fd8</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
@@ -3476,12 +3476,12 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
           <t>farm-ec0b7d9d631f8d4f</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -3535,12 +3535,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
           <t>farm-8a8152f932c5d9be</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
@@ -3602,12 +3602,12 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
           <t>farm-fa735715cecab592</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -3657,12 +3657,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
           <t>farm-672959abe86fb124</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
@@ -3716,12 +3716,12 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
           <t>farm-76f08cbd93b3d844</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -3783,12 +3783,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
           <t>farm-9f97203875cdca77</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
@@ -3850,12 +3850,12 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
           <t>farm-8ee5456e0e65f58a</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -3909,12 +3909,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
           <t>farm-5327150d4f98ad68</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
@@ -3968,12 +3968,12 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
           <t>farm-75c29f7703b46c97</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -4023,12 +4023,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
           <t>farm-4566b49ca9083900</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
@@ -4090,12 +4090,12 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
           <t>farm-3682da0dc3902abe</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
@@ -4149,12 +4149,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
           <t>farm-649c4594d0aa48d4</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
@@ -4208,12 +4208,12 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
           <t>farm-4b493339ea4ce070</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -4267,12 +4267,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
           <t>farm-3a8abf7414457cbf</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -4334,12 +4334,12 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
           <t>farm-24e27db91cb6706a</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -4393,12 +4393,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
           <t>farm-bb07e6718a046171</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -4460,12 +4460,12 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
           <t>farm-98967c23ce55809f</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
@@ -4519,12 +4519,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
           <t>farm-a83364b83ecf755e</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -4578,12 +4578,12 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
           <t>farm-e8dadd9945015af2</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -4645,12 +4645,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
           <t>farm-3db5b7cb2813b407</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -4704,12 +4704,12 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
           <t>farm-afa31abccc822ba4</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -4771,12 +4771,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
           <t>farm-124f3e0ec350120e</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -4830,12 +4830,12 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
           <t>farm-acd70914d8b017fd</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -4889,12 +4889,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
           <t>farm-32514ffd016d3887</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -4956,12 +4956,12 @@
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
           <t>farm-88f80f27ada8d52c</t>
-        </is>
-      </c>
-      <c r="B71" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
@@ -5047,12 +5047,12 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Farm UID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -5089,12 +5089,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
           <t>farm-952e3e7f9cce8bac</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
@@ -5125,12 +5125,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
           <t>farm-952e3e7f9cce8bac</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
@@ -5161,12 +5161,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
           <t>farm-952e3e7f9cce8bac</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -5197,12 +5197,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
           <t>farm-952e3e7f9cce8bac</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
@@ -5233,12 +5233,12 @@
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
           <t>farm-952e3e7f9cce8bac</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C6" s="16" t="n">
@@ -5269,12 +5269,12 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
           <t>farm-fb13b7efbe9e3f35</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -5305,12 +5305,12 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
           <t>farm-fb13b7efbe9e3f35</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
@@ -5341,12 +5341,12 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
           <t>farm-fb13b7efbe9e3f35</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -5377,12 +5377,12 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
           <t>farm-fb13b7efbe9e3f35</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
@@ -5413,12 +5413,12 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
           <t>farm-fb13b7efbe9e3f35</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
@@ -5449,12 +5449,12 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
           <t>farm-fb13b7efbe9e3f35</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -5485,12 +5485,12 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
           <t>farm-fb13b7efbe9e3f35</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -5521,12 +5521,12 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
           <t>farm-fb13b7efbe9e3f35</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
@@ -5557,12 +5557,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
           <t>farm-845d5252f2eca38f</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
@@ -5597,12 +5597,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>farm-845d5252f2eca38f</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -5633,12 +5633,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
           <t>farm-845d5252f2eca38f</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
@@ -5673,12 +5673,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>farm-845d5252f2eca38f</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -5713,12 +5713,12 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
           <t>farm-845d5252f2eca38f</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
@@ -5753,12 +5753,12 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
           <t>farm-78f45637e348bdaf</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
@@ -5789,12 +5789,12 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
           <t>farm-78f45637e348bdaf</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
@@ -5829,12 +5829,12 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
           <t>farm-78f45637e348bdaf</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
@@ -5865,12 +5865,12 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
           <t>farm-78f45637e348bdaf</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -5901,12 +5901,12 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
           <t>farm-78f45637e348bdaf</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
@@ -5937,12 +5937,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>farm-074eca694879aa6e</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -5973,12 +5973,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
           <t>farm-074eca694879aa6e</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -6009,12 +6009,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t>farm-074eca694879aa6e</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
@@ -6045,12 +6045,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>farm-074eca694879aa6e</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -6081,12 +6081,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
           <t>farm-074eca694879aa6e</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
@@ -6117,12 +6117,12 @@
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
           <t>farm-074eca694879aa6e</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C30" s="16" t="n">
@@ -6153,12 +6153,12 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
           <t>farm-85691d9be362dd92</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -6189,12 +6189,12 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
           <t>farm-85691d9be362dd92</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -6225,12 +6225,12 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
           <t>farm-85691d9be362dd92</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -6261,12 +6261,12 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
           <t>farm-85691d9be362dd92</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -6297,12 +6297,12 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>farm-85691d9be362dd92</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -6333,12 +6333,12 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
           <t>farm-85691d9be362dd92</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
@@ -6369,12 +6369,12 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
           <t>farm-85691d9be362dd92</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
@@ -6405,12 +6405,12 @@
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
           <t>farm-e1313b168a311d0b</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C38" s="16" t="n">
@@ -6441,12 +6441,12 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
           <t>farm-d1deabe5ee33721b</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -6477,12 +6477,12 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
           <t>farm-d1deabe5ee33721b</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -6513,12 +6513,12 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
           <t>farm-d1deabe5ee33721b</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
@@ -6549,12 +6549,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>farm-9384fa5d4c771974</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -6585,12 +6585,12 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
           <t>farm-9384fa5d4c771974</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
@@ -6621,12 +6621,12 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
           <t>farm-afc92ff8f440c5a0</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -6657,12 +6657,12 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
           <t>farm-afc92ff8f440c5a0</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -6693,12 +6693,12 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
           <t>farm-afc92ff8f440c5a0</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -6729,12 +6729,12 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
           <t>farm-afc92ff8f440c5a0</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -6765,12 +6765,12 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
           <t>farm-afc92ff8f440c5a0</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
@@ -6801,12 +6801,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
           <t>farm-2cde79d4f362fc20</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
@@ -6837,12 +6837,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
           <t>farm-2cde79d4f362fc20</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
@@ -6873,12 +6873,12 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
           <t>farm-2cde79d4f362fc20</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
@@ -6909,12 +6909,12 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
           <t>farm-b870c80169a03f88</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -6945,12 +6945,12 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
           <t>farm-b870c80169a03f88</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -6981,12 +6981,12 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
           <t>farm-b870c80169a03f88</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -7017,12 +7017,12 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
           <t>farm-b870c80169a03f88</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -7053,12 +7053,12 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
           <t>farm-b870c80169a03f88</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -7089,12 +7089,12 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
           <t>farm-b870c80169a03f88</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C57" s="12" t="n">
@@ -7125,12 +7125,12 @@
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
           <t>farm-8efe629438a3f81f</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C58" s="16" t="n">
@@ -7161,12 +7161,12 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
           <t>farm-6bb3e077f36e38b2</t>
-        </is>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
@@ -7197,12 +7197,12 @@
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
           <t>farm-f81d3c0b12219615</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C60" s="16" t="n">
@@ -7233,12 +7233,12 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
           <t>farm-07b8ef74bb489456</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -7269,12 +7269,12 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
           <t>farm-07b8ef74bb489456</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
@@ -7305,12 +7305,12 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
           <t>farm-07b8ef74bb489456</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
@@ -7341,12 +7341,12 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
           <t>farm-07b8ef74bb489456</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
@@ -7377,12 +7377,12 @@
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
           <t>farm-07b8ef74bb489456</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C65" s="12" t="n">
@@ -7413,12 +7413,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
           <t>farm-54146e89a448bd06</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -7449,12 +7449,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
           <t>farm-54146e89a448bd06</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -7485,12 +7485,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
           <t>farm-54146e89a448bd06</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -7521,12 +7521,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
           <t>farm-54146e89a448bd06</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -7557,12 +7557,12 @@
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
           <t>farm-54146e89a448bd06</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C70" s="16" t="n">
@@ -7593,12 +7593,12 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
           <t>farm-e5c279f4236b6189</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
@@ -7629,12 +7629,12 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
           <t>farm-e5c279f4236b6189</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
@@ -7665,12 +7665,12 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
           <t>farm-e5c279f4236b6189</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
@@ -7701,12 +7701,12 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
           <t>farm-e5c279f4236b6189</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -7737,12 +7737,12 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
           <t>farm-e5c279f4236b6189</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
@@ -7773,12 +7773,12 @@
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
           <t>farm-e5c279f4236b6189</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
@@ -7809,12 +7809,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
           <t>farm-8bdf78650621db28</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -7845,12 +7845,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
           <t>farm-8bdf78650621db28</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -7881,12 +7881,12 @@
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B79" s="16" t="inlineStr">
+        <is>
           <t>farm-8bdf78650621db28</t>
-        </is>
-      </c>
-      <c r="B79" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C79" s="16" t="n">
@@ -7917,12 +7917,12 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
           <t>farm-13959f39099f0e5f</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -7953,12 +7953,12 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
           <t>farm-13959f39099f0e5f</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -7989,12 +7989,12 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
           <t>farm-13959f39099f0e5f</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -8025,12 +8025,12 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
           <t>farm-13959f39099f0e5f</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -8061,12 +8061,12 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
           <t>farm-13959f39099f0e5f</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -8097,12 +8097,12 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
           <t>farm-13959f39099f0e5f</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -8137,12 +8137,12 @@
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
           <t>farm-13959f39099f0e5f</t>
-        </is>
-      </c>
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
@@ -8173,12 +8173,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
           <t>farm-6fca13195dca72af</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
@@ -8209,12 +8209,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
           <t>farm-6fca13195dca72af</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
@@ -8245,12 +8245,12 @@
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
           <t>farm-6fca13195dca72af</t>
-        </is>
-      </c>
-      <c r="B89" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C89" s="16" t="n">
@@ -8281,12 +8281,12 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
           <t>farm-c3fc573e5c4acba5</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
@@ -8317,12 +8317,12 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
           <t>farm-c3fc573e5c4acba5</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -8353,12 +8353,12 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
           <t>farm-c3fc573e5c4acba5</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -8389,12 +8389,12 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
           <t>farm-c3fc573e5c4acba5</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -8425,12 +8425,12 @@
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
           <t>farm-c3fc573e5c4acba5</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
@@ -8461,12 +8461,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
           <t>farm-c57fa3b9113fc7b7</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
@@ -8497,12 +8497,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
           <t>farm-c57fa3b9113fc7b7</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
@@ -8533,12 +8533,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
           <t>farm-c57fa3b9113fc7b7</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
@@ -8569,12 +8569,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
           <t>farm-c57fa3b9113fc7b7</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
@@ -8605,12 +8605,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
           <t>farm-c57fa3b9113fc7b7</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
@@ -8641,12 +8641,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
           <t>farm-c57fa3b9113fc7b7</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
@@ -8677,12 +8677,12 @@
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B101" s="16" t="inlineStr">
+        <is>
           <t>farm-c57fa3b9113fc7b7</t>
-        </is>
-      </c>
-      <c r="B101" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C101" s="16" t="n">
@@ -8713,12 +8713,12 @@
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
           <t>farm-79fc2a4c6da9eafa</t>
-        </is>
-      </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
@@ -8749,12 +8749,12 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
           <t>farm-79fc2a4c6da9eafa</t>
-        </is>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
@@ -8785,12 +8785,12 @@
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
           <t>farm-79fc2a4c6da9eafa</t>
-        </is>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
@@ -8821,12 +8821,12 @@
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
           <t>farm-79fc2a4c6da9eafa</t>
-        </is>
-      </c>
-      <c r="B105" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
@@ -8857,12 +8857,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
           <t>farm-f5449e374d877b37</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
@@ -8897,12 +8897,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
           <t>farm-f5449e374d877b37</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
@@ -8933,12 +8933,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
           <t>farm-f5449e374d877b37</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
@@ -8969,12 +8969,12 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
           <t>farm-f5449e374d877b37</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
@@ -9005,12 +9005,12 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
           <t>farm-f5449e374d877b37</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
@@ -9041,12 +9041,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
           <t>farm-f5449e374d877b37</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
@@ -9077,12 +9077,12 @@
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
           <t>farm-f5449e374d877b37</t>
-        </is>
-      </c>
-      <c r="B112" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C112" s="16" t="n">
@@ -9113,12 +9113,12 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
           <t>farm-e865e03867964311</t>
-        </is>
-      </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
@@ -9149,12 +9149,12 @@
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
           <t>farm-e865e03867964311</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C114" s="12" t="n">
@@ -9185,12 +9185,12 @@
     <row r="115">
       <c r="A115" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B115" s="16" t="inlineStr">
+        <is>
           <t>farm-a3294386b279337a</t>
-        </is>
-      </c>
-      <c r="B115" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C115" s="16" t="n">
@@ -9221,12 +9221,12 @@
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
           <t>farm-accb3fa2101c3789</t>
-        </is>
-      </c>
-      <c r="B116" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C116" s="12" t="n">
@@ -9257,12 +9257,12 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
           <t>farm-abdbf0576da99c8b</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
@@ -9293,12 +9293,12 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
           <t>farm-abdbf0576da99c8b</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
@@ -9329,12 +9329,12 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
           <t>farm-abdbf0576da99c8b</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
@@ -9365,12 +9365,12 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
           <t>farm-abdbf0576da99c8b</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
@@ -9401,12 +9401,12 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
           <t>farm-abdbf0576da99c8b</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
@@ -9437,12 +9437,12 @@
     <row r="122">
       <c r="A122" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B122" s="16" t="inlineStr">
+        <is>
           <t>farm-abdbf0576da99c8b</t>
-        </is>
-      </c>
-      <c r="B122" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C122" s="16" t="n">
@@ -9473,12 +9473,12 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
           <t>farm-cb9c2d243956a1cd</t>
-        </is>
-      </c>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
@@ -9509,12 +9509,12 @@
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
           <t>farm-cb9c2d243956a1cd</t>
-        </is>
-      </c>
-      <c r="B124" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C124" s="12" t="n">
@@ -9545,12 +9545,12 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
           <t>farm-cf5621f1257fd08b</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
@@ -9581,12 +9581,12 @@
     <row r="126">
       <c r="A126" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
           <t>farm-cf5621f1257fd08b</t>
-        </is>
-      </c>
-      <c r="B126" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C126" s="16" t="n">
@@ -9617,12 +9617,12 @@
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
           <t>farm-5abeeb94073a36a5</t>
-        </is>
-      </c>
-      <c r="B127" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C127" s="12" t="n">
@@ -9653,12 +9653,12 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
           <t>farm-5043b3493257a17e</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
@@ -9689,12 +9689,12 @@
     <row r="129">
       <c r="A129" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
           <t>farm-5043b3493257a17e</t>
-        </is>
-      </c>
-      <c r="B129" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C129" s="16" t="n">
@@ -9725,12 +9725,12 @@
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
           <t>farm-1c7e52d2eec151b1</t>
-        </is>
-      </c>
-      <c r="B130" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C130" s="12" t="n">
@@ -9761,12 +9761,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
           <t>farm-739bcdfb546d7819</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
@@ -9797,12 +9797,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
           <t>farm-739bcdfb546d7819</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
@@ -9833,12 +9833,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
           <t>farm-739bcdfb546d7819</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
@@ -9869,12 +9869,12 @@
     <row r="134">
       <c r="A134" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
           <t>farm-739bcdfb546d7819</t>
-        </is>
-      </c>
-      <c r="B134" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C134" s="16" t="n">
@@ -9905,12 +9905,12 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
           <t>farm-d2f56463641f55b6</t>
-        </is>
-      </c>
-      <c r="B135" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
@@ -9941,12 +9941,12 @@
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
           <t>farm-d2f56463641f55b6</t>
-        </is>
-      </c>
-      <c r="B136" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C136" s="8" t="n">
@@ -9977,12 +9977,12 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
           <t>farm-d2f56463641f55b6</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
@@ -10013,12 +10013,12 @@
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
           <t>farm-d2f56463641f55b6</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C138" s="8" t="n">
@@ -10049,12 +10049,12 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
           <t>farm-d2f56463641f55b6</t>
-        </is>
-      </c>
-      <c r="B139" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
@@ -10085,12 +10085,12 @@
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
           <t>farm-d2f56463641f55b6</t>
-        </is>
-      </c>
-      <c r="B140" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C140" s="12" t="n">
@@ -10121,12 +10121,12 @@
     <row r="141">
       <c r="A141" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
           <t>farm-aa14b1ecae53529a</t>
-        </is>
-      </c>
-      <c r="B141" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C141" s="16" t="n">
@@ -10157,12 +10157,12 @@
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
           <t>farm-2545beb9726fd83f</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C142" s="8" t="n">
@@ -10193,12 +10193,12 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
           <t>farm-2545beb9726fd83f</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
@@ -10229,12 +10229,12 @@
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
           <t>farm-2545beb9726fd83f</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C144" s="8" t="n">
@@ -10265,12 +10265,12 @@
     <row r="145">
       <c r="A145" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
           <t>farm-2545beb9726fd83f</t>
-        </is>
-      </c>
-      <c r="B145" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C145" s="12" t="n">
@@ -10301,12 +10301,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
           <t>farm-65eb57ca90edfc00</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C146" s="4" t="n">
@@ -10337,12 +10337,12 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
           <t>farm-65eb57ca90edfc00</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C147" s="4" t="n">
@@ -10373,12 +10373,12 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
           <t>farm-65eb57ca90edfc00</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C148" s="4" t="n">
@@ -10409,12 +10409,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
           <t>farm-65eb57ca90edfc00</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
@@ -10445,12 +10445,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
           <t>farm-65eb57ca90edfc00</t>
-        </is>
-      </c>
-      <c r="B150" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C150" s="4" t="n">
@@ -10481,12 +10481,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
           <t>farm-65eb57ca90edfc00</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C151" s="4" t="n">
@@ -10517,12 +10517,12 @@
     <row r="152">
       <c r="A152" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr">
+        <is>
           <t>farm-65eb57ca90edfc00</t>
-        </is>
-      </c>
-      <c r="B152" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C152" s="16" t="n">
@@ -10553,12 +10553,12 @@
     <row r="153">
       <c r="A153" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
           <t>farm-f32dec1621b342da</t>
-        </is>
-      </c>
-      <c r="B153" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C153" s="12" t="n">
@@ -10589,12 +10589,12 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
           <t>farm-316cd5378a884aec</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C154" s="4" t="n">
@@ -10625,12 +10625,12 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
           <t>farm-316cd5378a884aec</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C155" s="4" t="n">
@@ -10661,12 +10661,12 @@
     <row r="156">
       <c r="A156" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="inlineStr">
+        <is>
           <t>farm-316cd5378a884aec</t>
-        </is>
-      </c>
-      <c r="B156" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C156" s="16" t="n">
@@ -10697,12 +10697,12 @@
     <row r="157">
       <c r="A157" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
           <t>farm-a7055f2a67f08171</t>
-        </is>
-      </c>
-      <c r="B157" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C157" s="12" t="n">
@@ -10733,12 +10733,12 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
           <t>farm-2d6c5d61d9cedd64</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C158" s="4" t="n">
@@ -10769,12 +10769,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
           <t>farm-2d6c5d61d9cedd64</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C159" s="4" t="n">
@@ -10805,12 +10805,12 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
           <t>farm-2d6c5d61d9cedd64</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C160" s="4" t="n">
@@ -10841,12 +10841,12 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
           <t>farm-2d6c5d61d9cedd64</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C161" s="4" t="n">
@@ -10877,12 +10877,12 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
           <t>farm-2d6c5d61d9cedd64</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C162" s="4" t="n">
@@ -10913,12 +10913,12 @@
     <row r="163">
       <c r="A163" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
+        <is>
           <t>farm-2d6c5d61d9cedd64</t>
-        </is>
-      </c>
-      <c r="B163" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C163" s="16" t="n">
@@ -10949,12 +10949,12 @@
     <row r="164">
       <c r="A164" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
           <t>farm-4e02cf1e777043d5</t>
-        </is>
-      </c>
-      <c r="B164" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C164" s="8" t="n">
@@ -10985,12 +10985,12 @@
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
           <t>farm-4e02cf1e777043d5</t>
-        </is>
-      </c>
-      <c r="B165" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
@@ -11021,12 +11021,12 @@
     <row r="166">
       <c r="A166" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
           <t>farm-4e02cf1e777043d5</t>
-        </is>
-      </c>
-      <c r="B166" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C166" s="8" t="n">
@@ -11057,12 +11057,12 @@
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
           <t>farm-4e02cf1e777043d5</t>
-        </is>
-      </c>
-      <c r="B167" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
@@ -11093,12 +11093,12 @@
     <row r="168">
       <c r="A168" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
           <t>farm-4e02cf1e777043d5</t>
-        </is>
-      </c>
-      <c r="B168" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C168" s="8" t="n">
@@ -11129,12 +11129,12 @@
     <row r="169">
       <c r="A169" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="inlineStr">
+        <is>
           <t>farm-4e02cf1e777043d5</t>
-        </is>
-      </c>
-      <c r="B169" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C169" s="12" t="n">
@@ -11165,12 +11165,12 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
           <t>farm-dea55e991a4e7fd8</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C170" s="4" t="n">
@@ -11201,12 +11201,12 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
           <t>farm-dea55e991a4e7fd8</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C171" s="4" t="n">
@@ -11237,12 +11237,12 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
           <t>farm-dea55e991a4e7fd8</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C172" s="4" t="n">
@@ -11273,12 +11273,12 @@
     <row r="173">
       <c r="A173" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B173" s="16" t="inlineStr">
+        <is>
           <t>farm-dea55e991a4e7fd8</t>
-        </is>
-      </c>
-      <c r="B173" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C173" s="16" t="n">
@@ -11309,12 +11309,12 @@
     <row r="174">
       <c r="A174" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
           <t>farm-ec0b7d9d631f8d4f</t>
-        </is>
-      </c>
-      <c r="B174" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C174" s="8" t="n">
@@ -11345,12 +11345,12 @@
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
           <t>farm-ec0b7d9d631f8d4f</t>
-        </is>
-      </c>
-      <c r="B175" s="8" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
@@ -11381,12 +11381,12 @@
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B176" s="12" t="inlineStr">
+        <is>
           <t>farm-ec0b7d9d631f8d4f</t>
-        </is>
-      </c>
-      <c r="B176" s="12" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C176" s="12" t="n">
@@ -11417,12 +11417,12 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
           <t>farm-8a8152f932c5d9be</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C177" s="4" t="n">
@@ -11453,12 +11453,12 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
           <t>farm-8a8152f932c5d9be</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C178" s="4" t="n">
@@ -11489,12 +11489,12 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
           <t>farm-8a8152f932c5d9be</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C179" s="4" t="n">
@@ -11525,12 +11525,12 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
           <t>farm-8a8152f932c5d9be</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C180" s="4" t="n">
@@ -11561,12 +11561,12 @@
     <row r="181">
       <c r="A181" s="16" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B181" s="16" t="inlineStr">
+        <is>
           <t>farm-8a8152f932c5d9be</t>
-        </is>
-      </c>
-      <c r="B181" s="16" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C181" s="16" t="n">
@@ -11597,12 +11597,12 @@
     <row r="182">
       <c r="A182" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
           <t>farm-fa735715cecab592</t>
-        </is>
-      </c>
-      <c r="B182" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C182" s="8" t="n">
@@ -11633,12 +11633,12 @@
     <row r="183">
       <c r="A183" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
           <t>farm-fa735715cecab592</t>
-        </is>
-      </c>
-      <c r="B183" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
@@ -11669,12 +11669,12 @@
     <row r="184">
       <c r="A184" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
           <t>farm-fa735715cecab592</t>
-        </is>
-      </c>
-      <c r="B184" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C184" s="8" t="n">
@@ -11705,12 +11705,12 @@
     <row r="185">
       <c r="A185" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
           <t>farm-fa735715cecab592</t>
-        </is>
-      </c>
-      <c r="B185" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
@@ -11741,12 +11741,12 @@
     <row r="186">
       <c r="A186" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
           <t>farm-fa735715cecab592</t>
-        </is>
-      </c>
-      <c r="B186" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C186" s="8" t="n">
@@ -11777,12 +11777,12 @@
     <row r="187">
       <c r="A187" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B187" s="12" t="inlineStr">
+        <is>
           <t>farm-fa735715cecab592</t>
-        </is>
-      </c>
-      <c r="B187" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C187" s="12" t="n">
@@ -11813,12 +11813,12 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
           <t>farm-672959abe86fb124</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C188" s="4" t="n">
@@ -11849,12 +11849,12 @@
     <row r="189">
       <c r="A189" s="16" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B189" s="16" t="inlineStr">
+        <is>
           <t>farm-672959abe86fb124</t>
-        </is>
-      </c>
-      <c r="B189" s="16" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C189" s="16" t="n">
@@ -11885,12 +11885,12 @@
     <row r="190">
       <c r="A190" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B190" s="8" t="inlineStr">
+        <is>
           <t>farm-76f08cbd93b3d844</t>
-        </is>
-      </c>
-      <c r="B190" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C190" s="8" t="n">
@@ -11921,12 +11921,12 @@
     <row r="191">
       <c r="A191" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
           <t>farm-76f08cbd93b3d844</t>
-        </is>
-      </c>
-      <c r="B191" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
@@ -11957,12 +11957,12 @@
     <row r="192">
       <c r="A192" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
           <t>farm-76f08cbd93b3d844</t>
-        </is>
-      </c>
-      <c r="B192" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C192" s="8" t="n">
@@ -11993,12 +11993,12 @@
     <row r="193">
       <c r="A193" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
           <t>farm-76f08cbd93b3d844</t>
-        </is>
-      </c>
-      <c r="B193" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
@@ -12029,12 +12029,12 @@
     <row r="194">
       <c r="A194" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
           <t>farm-76f08cbd93b3d844</t>
-        </is>
-      </c>
-      <c r="B194" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C194" s="8" t="n">
@@ -12065,12 +12065,12 @@
     <row r="195">
       <c r="A195" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
           <t>farm-76f08cbd93b3d844</t>
-        </is>
-      </c>
-      <c r="B195" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
@@ -12101,12 +12101,12 @@
     <row r="196">
       <c r="A196" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B196" s="8" t="inlineStr">
+        <is>
           <t>farm-76f08cbd93b3d844</t>
-        </is>
-      </c>
-      <c r="B196" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C196" s="8" t="n">
@@ -12137,12 +12137,12 @@
     <row r="197">
       <c r="A197" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B197" s="8" t="inlineStr">
+        <is>
           <t>farm-76f08cbd93b3d844</t>
-        </is>
-      </c>
-      <c r="B197" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
@@ -12173,12 +12173,12 @@
     <row r="198">
       <c r="A198" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B198" s="12" t="inlineStr">
+        <is>
           <t>farm-76f08cbd93b3d844</t>
-        </is>
-      </c>
-      <c r="B198" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C198" s="12" t="n">
@@ -12209,12 +12209,12 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
           <t>farm-9f97203875cdca77</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C199" s="4" t="n">
@@ -12245,12 +12245,12 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
           <t>farm-9f97203875cdca77</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C200" s="4" t="n">
@@ -12281,12 +12281,12 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
           <t>farm-9f97203875cdca77</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C201" s="4" t="n">
@@ -12317,12 +12317,12 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
           <t>farm-9f97203875cdca77</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C202" s="4" t="n">
@@ -12353,12 +12353,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
           <t>farm-9f97203875cdca77</t>
-        </is>
-      </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C203" s="4" t="n">
@@ -12389,12 +12389,12 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
           <t>farm-9f97203875cdca77</t>
-        </is>
-      </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C204" s="4" t="n">
@@ -12425,12 +12425,12 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
           <t>farm-9f97203875cdca77</t>
-        </is>
-      </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C205" s="4" t="n">
@@ -12461,12 +12461,12 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
           <t>farm-9f97203875cdca77</t>
-        </is>
-      </c>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C206" s="4" t="n">
@@ -12497,12 +12497,12 @@
     <row r="207">
       <c r="A207" s="16" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B207" s="16" t="inlineStr">
+        <is>
           <t>farm-9f97203875cdca77</t>
-        </is>
-      </c>
-      <c r="B207" s="16" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C207" s="16" t="n">
@@ -12533,12 +12533,12 @@
     <row r="208">
       <c r="A208" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B208" s="12" t="inlineStr">
+        <is>
           <t>farm-8ee5456e0e65f58a</t>
-        </is>
-      </c>
-      <c r="B208" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C208" s="12" t="n">
@@ -12569,12 +12569,12 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
           <t>farm-5327150d4f98ad68</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C209" s="4" t="n">
@@ -12605,12 +12605,12 @@
     <row r="210">
       <c r="A210" s="16" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B210" s="16" t="inlineStr">
+        <is>
           <t>farm-5327150d4f98ad68</t>
-        </is>
-      </c>
-      <c r="B210" s="16" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C210" s="16" t="n">
@@ -12641,12 +12641,12 @@
     <row r="211">
       <c r="A211" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B211" s="12" t="inlineStr">
+        <is>
           <t>farm-75c29f7703b46c97</t>
-        </is>
-      </c>
-      <c r="B211" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C211" s="12" t="n">
@@ -12677,12 +12677,12 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
           <t>farm-4566b49ca9083900</t>
-        </is>
-      </c>
-      <c r="B212" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C212" s="4" t="n">
@@ -12713,12 +12713,12 @@
     <row r="213">
       <c r="A213" s="16" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B213" s="16" t="inlineStr">
+        <is>
           <t>farm-4566b49ca9083900</t>
-        </is>
-      </c>
-      <c r="B213" s="16" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C213" s="16" t="n">
@@ -12749,12 +12749,12 @@
     <row r="214">
       <c r="A214" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B214" s="12" t="inlineStr">
+        <is>
           <t>farm-3682da0dc3902abe</t>
-        </is>
-      </c>
-      <c r="B214" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C214" s="12" t="n">
@@ -12785,12 +12785,12 @@
     <row r="215">
       <c r="A215" s="16" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B215" s="16" t="inlineStr">
+        <is>
           <t>farm-649c4594d0aa48d4</t>
-        </is>
-      </c>
-      <c r="B215" s="16" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C215" s="16" t="n">
@@ -12821,12 +12821,12 @@
     <row r="216">
       <c r="A216" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B216" s="12" t="inlineStr">
+        <is>
           <t>farm-4b493339ea4ce070</t>
-        </is>
-      </c>
-      <c r="B216" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C216" s="12" t="n">
@@ -12857,12 +12857,12 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
           <t>farm-3a8abf7414457cbf</t>
-        </is>
-      </c>
-      <c r="B217" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C217" s="4" t="n">
@@ -12893,12 +12893,12 @@
     <row r="218">
       <c r="A218" s="16" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B218" s="16" t="inlineStr">
+        <is>
           <t>farm-3a8abf7414457cbf</t>
-        </is>
-      </c>
-      <c r="B218" s="16" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C218" s="16" t="n">
@@ -12929,12 +12929,12 @@
     <row r="219">
       <c r="A219" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
+        <is>
           <t>farm-24e27db91cb6706a</t>
-        </is>
-      </c>
-      <c r="B219" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
@@ -12965,12 +12965,12 @@
     <row r="220">
       <c r="A220" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B220" s="12" t="inlineStr">
+        <is>
           <t>farm-24e27db91cb6706a</t>
-        </is>
-      </c>
-      <c r="B220" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C220" s="12" t="n">
@@ -13001,12 +13001,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
           <t>farm-bb07e6718a046171</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C221" s="4" t="n">
@@ -13037,12 +13037,12 @@
     <row r="222">
       <c r="A222" s="16" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B222" s="16" t="inlineStr">
+        <is>
           <t>farm-bb07e6718a046171</t>
-        </is>
-      </c>
-      <c r="B222" s="16" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C222" s="16" t="n">
@@ -13073,12 +13073,12 @@
     <row r="223">
       <c r="A223" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
           <t>farm-98967c23ce55809f</t>
-        </is>
-      </c>
-      <c r="B223" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
@@ -13109,12 +13109,12 @@
     <row r="224">
       <c r="A224" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B224" s="8" t="inlineStr">
+        <is>
           <t>farm-98967c23ce55809f</t>
-        </is>
-      </c>
-      <c r="B224" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C224" s="8" t="n">
@@ -13145,12 +13145,12 @@
     <row r="225">
       <c r="A225" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B225" s="12" t="inlineStr">
+        <is>
           <t>farm-98967c23ce55809f</t>
-        </is>
-      </c>
-      <c r="B225" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C225" s="12" t="n">
@@ -13181,12 +13181,12 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
           <t>farm-a83364b83ecf755e</t>
-        </is>
-      </c>
-      <c r="B226" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C226" s="4" t="n">
@@ -13217,12 +13217,12 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
           <t>farm-a83364b83ecf755e</t>
-        </is>
-      </c>
-      <c r="B227" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C227" s="4" t="n">
@@ -13253,12 +13253,12 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
           <t>farm-a83364b83ecf755e</t>
-        </is>
-      </c>
-      <c r="B228" s="4" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C228" s="4" t="n">
@@ -13289,12 +13289,12 @@
     <row r="229">
       <c r="A229" s="16" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B229" s="16" t="inlineStr">
+        <is>
           <t>farm-a83364b83ecf755e</t>
-        </is>
-      </c>
-      <c r="B229" s="16" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C229" s="16" t="n">
@@ -13325,12 +13325,12 @@
     <row r="230">
       <c r="A230" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B230" s="8" t="inlineStr">
+        <is>
           <t>farm-e8dadd9945015af2</t>
-        </is>
-      </c>
-      <c r="B230" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C230" s="8" t="n">
@@ -13361,12 +13361,12 @@
     <row r="231">
       <c r="A231" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B231" s="12" t="inlineStr">
+        <is>
           <t>farm-e8dadd9945015af2</t>
-        </is>
-      </c>
-      <c r="B231" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C231" s="12" t="n">
@@ -13397,12 +13397,12 @@
     <row r="232">
       <c r="A232" s="16" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B232" s="16" t="inlineStr">
+        <is>
           <t>farm-3db5b7cb2813b407</t>
-        </is>
-      </c>
-      <c r="B232" s="16" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C232" s="16" t="n">
@@ -13433,12 +13433,12 @@
     <row r="233">
       <c r="A233" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
+        <is>
           <t>farm-afa31abccc822ba4</t>
-        </is>
-      </c>
-      <c r="B233" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C233" s="8" t="n">
@@ -13469,12 +13469,12 @@
     <row r="234">
       <c r="A234" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B234" s="12" t="inlineStr">
+        <is>
           <t>farm-afa31abccc822ba4</t>
-        </is>
-      </c>
-      <c r="B234" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C234" s="12" t="n">
@@ -13505,12 +13505,12 @@
     <row r="235">
       <c r="A235" s="16" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B235" s="16" t="inlineStr">
+        <is>
           <t>farm-124f3e0ec350120e</t>
-        </is>
-      </c>
-      <c r="B235" s="16" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C235" s="16" t="n">
@@ -13541,12 +13541,12 @@
     <row r="236">
       <c r="A236" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B236" s="8" t="inlineStr">
+        <is>
           <t>farm-acd70914d8b017fd</t>
-        </is>
-      </c>
-      <c r="B236" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C236" s="8" t="n">
@@ -13577,12 +13577,12 @@
     <row r="237">
       <c r="A237" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
+        <is>
           <t>farm-acd70914d8b017fd</t>
-        </is>
-      </c>
-      <c r="B237" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
@@ -13613,12 +13613,12 @@
     <row r="238">
       <c r="A238" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B238" s="8" t="inlineStr">
+        <is>
           <t>farm-acd70914d8b017fd</t>
-        </is>
-      </c>
-      <c r="B238" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C238" s="8" t="n">
@@ -13649,12 +13649,12 @@
     <row r="239">
       <c r="A239" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
           <t>farm-acd70914d8b017fd</t>
-        </is>
-      </c>
-      <c r="B239" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
@@ -13685,12 +13685,12 @@
     <row r="240">
       <c r="A240" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B240" s="12" t="inlineStr">
+        <is>
           <t>farm-acd70914d8b017fd</t>
-        </is>
-      </c>
-      <c r="B240" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C240" s="12" t="n">
@@ -13721,12 +13721,12 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
           <t>farm-32514ffd016d3887</t>
-        </is>
-      </c>
-      <c r="B241" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C241" s="4" t="n">
@@ -13757,12 +13757,12 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
           <t>farm-32514ffd016d3887</t>
-        </is>
-      </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C242" s="4" t="n">
@@ -13793,12 +13793,12 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
           <t>farm-32514ffd016d3887</t>
-        </is>
-      </c>
-      <c r="B243" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C243" s="4" t="n">
@@ -13829,12 +13829,12 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
           <t>farm-32514ffd016d3887</t>
-        </is>
-      </c>
-      <c r="B244" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C244" s="4" t="n">
@@ -13865,12 +13865,12 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
           <t>farm-32514ffd016d3887</t>
-        </is>
-      </c>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C245" s="4" t="n">
@@ -13901,12 +13901,12 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
           <t>farm-32514ffd016d3887</t>
-        </is>
-      </c>
-      <c r="B246" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C246" s="4" t="n">
@@ -13937,12 +13937,12 @@
     <row r="247">
       <c r="A247" s="16" t="inlineStr">
         <is>
+          <t>Mangrove_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B247" s="16" t="inlineStr">
+        <is>
           <t>farm-32514ffd016d3887</t>
-        </is>
-      </c>
-      <c r="B247" s="16" t="inlineStr">
-        <is>
-          <t>Mangrove_labels2.shp</t>
         </is>
       </c>
       <c r="C247" s="16" t="n">
@@ -13973,12 +13973,12 @@
     <row r="248">
       <c r="A248" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B248" s="8" t="inlineStr">
+        <is>
           <t>farm-88f80f27ada8d52c</t>
-        </is>
-      </c>
-      <c r="B248" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C248" s="8" t="n">
@@ -14009,12 +14009,12 @@
     <row r="249">
       <c r="A249" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="inlineStr">
+        <is>
           <t>farm-88f80f27ada8d52c</t>
-        </is>
-      </c>
-      <c r="B249" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
@@ -14045,12 +14045,12 @@
     <row r="250">
       <c r="A250" s="8" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B250" s="8" t="inlineStr">
+        <is>
           <t>farm-88f80f27ada8d52c</t>
-        </is>
-      </c>
-      <c r="B250" s="8" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C250" s="8" t="n">
@@ -14081,12 +14081,12 @@
     <row r="251">
       <c r="A251" s="12" t="inlineStr">
         <is>
+          <t>Caniaba_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B251" s="12" t="inlineStr">
+        <is>
           <t>farm-88f80f27ada8d52c</t>
-        </is>
-      </c>
-      <c r="B251" s="12" t="inlineStr">
-        <is>
-          <t>Caniaba_labels2.shp</t>
         </is>
       </c>
       <c r="C251" s="12" t="n">
